--- a/docs/downloads/12/tbl_pro1_marovoay_tous.xlsx
+++ b/docs/downloads/12/tbl_pro1_marovoay_tous.xlsx
@@ -362,27 +362,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
     </row>
